--- a/02_加值成品/八上/八上6-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上6-2_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上6-2 元素與週期表　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二上學期 八上6-2 元素與週期表　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>氫的元素符號是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>汞(Hg)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>He</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>非金屬</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>常見</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>氧的元素符號是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>原子序</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>週期</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>光澤導電延展</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>常見</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>鐵的元素符號是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>大寫</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>He</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>Fe</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>金屬</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>週期表依什麼排列？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>門得列夫</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>光澤導電延展</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>He</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>原子序</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>質子數</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>金屬有什麼特性？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>光澤導電延展</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>典型</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>週期表的直行稱？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>族</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>汞(Hg)</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>光澤導電延展</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>性質相似</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>元素符號首字母要？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>大寫</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>門得列夫</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>週期</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>規則</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>地殼含量最多的元素？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>金屬</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>氧</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>He</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>最多</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>氦的元素符號是？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>He</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>汞(Hg)</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>惰性氣體</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>金的元素符號是？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>Na</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>不導電</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>半導體</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>Au</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>金屬</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上6-2 元素與週期表　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二上學期 八上6-2 元素與週期表　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>鈉的元素符號是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Na</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>金屬</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>碳的元素符號是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>原子序</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>氧</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>非金屬</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>同一族元素性質如何？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>相似</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>光澤導電延展</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>直行</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>常溫液態的金屬是？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>汞(Hg)</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>門得列夫</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>氧</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>特例</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>非金屬多半導電嗎？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>不導電</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>He</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>氮</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>絕緣</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>週期表橫列稱？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>汞(Hg)</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>週期</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>氧</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>原子序遞增</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>空氣中含量最多元素？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>相似</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>原子序</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>週期</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>氮</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>約78%</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>銅Cu屬於金屬還非金屬？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>Na</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>金屬</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>不導電</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>導電</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>鎂Mg屬於金屬還非金屬？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>不導電</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>光澤導電延展</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>金屬</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>金屬</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>氯Cl屬於金屬還非金屬？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>非金屬</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>門得列夫</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>Na</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>非金屬</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上6-2 元素與週期表　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二上學期 八上6-2 元素與週期表　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>為何同族元素化學性質相似？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>最外層電子數相同</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>金屬延展性可重塑</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>同族性質相似可推測</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>最外層電子已滿</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>電子組態</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>金屬能導電是因為？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>最外層電子數相同</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>氧與矽(如砂石)</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>金屬鍵允許原子層滑動</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>有可自由移動的電子</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>自由電子</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>週期表由誰系統化提出？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Na</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>門得列夫</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>週期律</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>原子序17與19誰較活潑(金屬性)？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>最外層電子已滿</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>金屬延展性可重塑</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>同族性質相似可推測</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>19(鉀)偏金屬</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>趨勢</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>類金屬如矽的用途？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>半導體</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>金屬</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Fe</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>性質介於</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>為何鋁罐可回收再製？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>金屬延展性可重塑</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>最外層電子已滿</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>19(鉀)偏金屬</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>有可自由移動的電子</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>特性</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>惰性氣體不易反應因為？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>同族性質相似可推測</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>氧與矽(如砂石)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>金屬鍵允許原子層滑動</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>最外層電子已滿</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>穩定</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>由地殼組成推知建材主要元素？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>19(鉀)偏金屬</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>同族性質相似可推測</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>氧與矽(如砂石)</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>金屬延展性可重塑</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>含量</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何金屬多具延展性可打成薄片？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>同族性質相似可推測</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>有可自由移動的電子</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>金屬鍵允許原子層滑動</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>19(鉀)偏金屬</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>延展</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>週期表如何幫助預測元素性質？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>同族性質相似可推測</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>有可自由移動的電子</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>最外層電子數相同</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>金屬延展性可重塑</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>週期律</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八上/八上6-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上6-2_三種難度測驗卷.xlsx
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>金屬延展性可重塑</t>
+          <t>金屬可重複熔化鑄造成新產品</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -1630,37 +1630,37 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>原子序17與19誰較活潑(金屬性)？</t>
+          <t>原子序11(鈉)與19(鉀)同屬第一族，誰的金屬性較強？</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>最外層電子已滿</t>
+          <t>最外層電子數相同</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>金屬延展性可重塑</t>
+          <t>金屬鍵允許原子層滑動</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>同族性質相似可推測</t>
+          <t>19(鉀)較強</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>19(鉀)偏金屬</t>
+          <t>金屬可重複熔化鑄造成新產品</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>趨勢</t>
+          <t>同族由上而下金屬性遞增</t>
         </is>
       </c>
     </row>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>金屬延展性可重塑</t>
+          <t>金屬可重複熔化鑄造成新產品</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>19(鉀)偏金屬</t>
+          <t>19(鉀)較強</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>特性</t>
+          <t>熔煉再製</t>
         </is>
       </c>
     </row>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>19(鉀)偏金屬</t>
+          <t>19(鉀)較強</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>金屬延展性可重塑</t>
+          <t>金屬可重複熔化鑄造成新產品</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>19(鉀)偏金屬</t>
+          <t>19(鉀)較強</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>金屬延展性可重塑</t>
+          <t>金屬可重複熔化鑄造成新產品</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">

--- a/02_加值成品/八上/八上6-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上6-2_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>常見</t>
+          <t>常見：氫是最輕的元素，元素符號寫作H</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>常見</t>
+          <t>常見：氧是地殼和空氣中常見的元素，元素符號寫作O</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>金屬</t>
+          <t>金屬：鐵是常見的金屬元素，元素符號寫作Fe，來自拉丁文ferrum</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>質子數</t>
+          <t>質子數：週期表是依照原子序(也就是質子數)由小到大依序排列的</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>典型</t>
+          <t>典型：金屬元素通常具有金屬光澤、良好的導電導熱性，以及可以延展加工的特性</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>性質相似</t>
+          <t>性質相似：週期表中直行排列的元素稱為同一族，同族元素通常化學性質相似</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>規則</t>
+          <t>規則：元素符號的第一個字母依規定要寫成大寫，若有第二個字母則要寫小寫</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>最多</t>
+          <t>最多：氧是地殼中含量最豐富的元素，許多岩石礦物都含有大量的氧</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>惰性氣體</t>
+          <t>惰性氣體：氦是一種惰性氣體，元素符號寫作He</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>金屬</t>
+          <t>金屬：金是一種金屬元素，元素符號寫作Au，來自拉丁文aurum</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>金屬</t>
+          <t>金屬：鈉是活性很大的金屬元素，元素符號寫作Na，來自拉丁文natrium</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>非金屬</t>
+          <t>非金屬：碳是常見的非金屬元素，元素符號寫作C，是有機化合物的基礎</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>直行</t>
+          <t>直行：週期表中同一直行(同族)的元素，最外層電子數相同，化學性質通常相似</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>特例</t>
+          <t>特例：汞是唯一在常溫下呈液態的金屬，多數金屬在常溫下都是固態</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>絕緣</t>
+          <t>絕緣：非金屬元素大多不容易導電，屬於電的不良導體(絕緣體)，這和金屬性質明顯不同</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>原子序遞增</t>
+          <t>原子序遞增：週期表中橫向排列的一列稱為一個週期，同一週期內原子序由左到右依序遞增</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>約78%</t>
+          <t>約78%：空氣中含量最多的成分是氮氣，大約佔了空氣體積的78%</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>導電</t>
+          <t>導電：銅具有良好的導電性和金屬光澤，屬於金屬元素，常用來製作電線</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>金屬</t>
+          <t>金屬：鎂在週期表中屬於金屬元素，具有金屬光澤、能導電導熱等金屬特性</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>非金屬</t>
+          <t>非金屬：氯在週期表中屬於非金屬元素，性質與金屬明顯不同</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>電子組態</t>
+          <t>電子組態：同族元素的最外層電子數目相同，而化學性質主要由最外層電子決定，所以同族元素化學性質相似</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>自由電子</t>
+          <t>自由電子：金屬原子的最外層電子容易脫離，在金屬內部形成可以自由移動的電子，這些自由電子能傳導電流</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>週期律</t>
+          <t>週期律：門得列夫依照元素性質的規律性，把已知元素系統化排列成週期表，並成功預測了當時尚未發現的元素</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>性質介於</t>
+          <t>性質介於：矽的性質介於金屬與非金屬之間，導電性可以被調控，是製造電腦晶片等半導體元件的重要材料</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>熔煉再製</t>
+          <t>熔煉再製：金屬可以重複熔化、鑄造成新產品而不會改變元素本質，所以鋁罐能不斷回收再製造成新的鋁製品</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>穩定</t>
+          <t>穩定：惰性氣體的最外層電子已經填滿達到穩定結構，不容易再和其他原子產生反應</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>含量</t>
+          <t>含量：地殼中含量最多的兩種元素是氧和矽，砂石等常見建材的主要成分正好含有大量的氧與矽</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>延展</t>
+          <t>延展：金屬原子之間以金屬鍵結合，這種鍵結允許原子層與層之間互相滑動而不斷裂，所以金屬容易被敲打延展成薄片或拉成細絲</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>週期律</t>
+          <t>週期律：週期表把化學性質相似的元素排在同一直行(同族)，只要知道某元素的性質，就可以推測同族其他元素可能具有相似的性質</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八上/八上6-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上6-2_三種難度測驗卷.xlsx
@@ -563,17 +563,17 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>汞(Hg)</t>
+          <t>Fe</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>He</t>
+          <t>光澤導電延展</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>非金屬</t>
+          <t>門得列夫</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -888,17 +888,17 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>原子序</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>汞(Hg)</t>
+          <t>光澤導電延展</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>氧</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -1169,12 +1169,12 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>門得列夫</t>
+          <t>原子序</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>氧</t>
+          <t>週期</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -1319,14 +1319,14 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
+          <t>相似</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>Na</t>
-        </is>
-      </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
           <t>金屬</t>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>不導電</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -1359,12 +1359,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>不導電</t>
+          <t>原子序</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>光澤導電延展</t>
+          <t>大寫</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Fe</t>
+          <t>O</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1404,17 +1404,17 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>門得列夫</t>
+          <t>不導電</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Na</t>
+          <t>族</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>Au</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
